--- a/EBOM/bom_web/data/pel_code_master.xlsx
+++ b/EBOM/bom_web/data/pel_code_master.xlsx
@@ -451,18 +451,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8811C1</t>
+          <t>882CA1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLOTH1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>H_P_COVER</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Headrest_PLASTIC COVER</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>공용</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -474,20 +478,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8811C2 </t>
+          <t>882ZA1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLOTH2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>공용</t>
-        </is>
-      </c>
+          <t>RLX</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RELAXION SEAT - PREMIUM RELAXION SEAT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,22 +501,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8811B4</t>
+          <t>885DA1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A/CLOTH</t>
+          <t>SLID'G</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A/CLOTH(CLOTH+ARTIFICIAL LEATHER)</t>
+          <t>CUSH MECH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>공용</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -524,22 +528,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8811E2</t>
+          <t>885EA2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P/LEA</t>
+          <t>D_RECL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pure Leather</t>
+          <t>DOUBLE RECLING</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>공용</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -551,22 +555,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8811F2</t>
+          <t>885IA1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A/LEA(1)</t>
+          <t xml:space="preserve">FOLD'G </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial Leather(ONE TONE) </t>
+          <t>SEAT BACK FOLDING</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>공용</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -578,22 +582,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8811F3</t>
+          <t>885JA1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A/LEA(2)</t>
+          <t>W/IN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial Leather(TWO TONE) </t>
+          <t>WALK IN S/W</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>공용</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -605,22 +609,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8821A1 </t>
+          <t>885NA1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>H_UP/DN</t>
+          <t xml:space="preserve">VENT </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Headrest</t>
+          <t>AIR VENTILATION SEAT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -632,22 +636,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8821A5</t>
+          <t>885PA1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>H_SLID'G</t>
+          <t xml:space="preserve">TABLE  </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Headrest</t>
+          <t>FOLD UP TRAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -659,22 +663,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>882CA1</t>
+          <t>886BA1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>H_P_COVER</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Headrest_PLASTIC COVER</t>
-        </is>
-      </c>
+          <t>B/POCKET</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -686,22 +686,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8823A1 </t>
+          <t>886BA3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SLID'G</t>
+          <t>B/PNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CUSH MECH</t>
+          <t>W/POCKET</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -713,22 +713,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">8823B2 </t>
+          <t>888AA2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOWEL BAR TYPE</t>
+          <t>P_TENSNR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CUSH MECH</t>
+          <t>ELECTRICAL TYPE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>안전부품</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">8824A2 </t>
+          <t>888DA1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D_RECL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MNL</t>
-        </is>
-      </c>
+          <t>SBR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>안전부품</t>
         </is>
       </c>
     </row>
@@ -767,24 +763,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8825A2</t>
+          <t>961SA3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>H_ADJ</t>
+          <t>USB(27W)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MNL</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>운전석</t>
-        </is>
-      </c>
+          <t>1PORT(2EA)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -794,22 +786,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8827A1 </t>
+          <t xml:space="preserve">5693A1 </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PWR </t>
+          <t xml:space="preserve">THORAX </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>SIDE AIR BAG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>안전부품</t>
         </is>
       </c>
     </row>
@@ -821,22 +813,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8827A3 </t>
+          <t>5693A3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IMS</t>
+          <t>T &amp; P</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>SIDE AIR BAG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>안전부품</t>
         </is>
       </c>
     </row>
@@ -848,24 +840,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8828A2</t>
+          <t>5699A1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L/SUPT</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PWR</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>운전석</t>
-        </is>
-      </c>
+          <t>CENTER SIDE AIR BAG</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -875,22 +863,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8828A6 </t>
+          <t>8811B4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2WAY L/SUPT</t>
+          <t>A/CLOTH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>A/CLOTH(CLOTH+ARTIFICIAL LEATHER)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>공용</t>
         </is>
       </c>
     </row>
@@ -902,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8836A1 </t>
+          <t>8811C1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B/POCKET</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SEAT BACK POCKET</t>
-        </is>
-      </c>
+          <t>CLOTH1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>공용</t>
         </is>
       </c>
     </row>
@@ -929,22 +913,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8836A3</t>
+          <t xml:space="preserve">8811C2 </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B/PNL</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>W/POCKET</t>
-        </is>
-      </c>
+          <t>CLOTH2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>공용</t>
         </is>
       </c>
     </row>
@@ -956,22 +936,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8838B3</t>
+          <t>8811E2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HTR(2STEP)</t>
+          <t>P/LEA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HTR(HIGH/LOW)</t>
+          <t>Pure Leather</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>공용</t>
         </is>
       </c>
     </row>
@@ -983,22 +963,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8838B4</t>
+          <t>8811F2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HTR(3STEP)</t>
+          <t>A/LEA(1)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3-STEPS(BUTTON)</t>
+          <t xml:space="preserve">Artificial Leather(ONE TONE) </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>공용</t>
         </is>
       </c>
     </row>
@@ -1010,18 +990,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8839A1</t>
+          <t>8811F3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EASY ACCESS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>A/LEA(2)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial Leather(TWO TONE) </t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>운전석</t>
+          <t>공용</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1017,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8841A1</t>
+          <t>8821A1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VENT</t>
+          <t>H_UP/DN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AIR VENTILATION SEAT</t>
+          <t>UP/DOWN_2Way</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1060,17 +1044,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8845A1</t>
+          <t>8821A5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TABLE  </t>
+          <t>H_SLID'G</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FOLD UP TRAY</t>
+          <t>UP/DOWN &amp; SLIDING</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1087,24 +1071,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8847A2</t>
+          <t>8821B1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P_EXT</t>
+          <t>4WAY H/REST (MESH)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EXTENDABLE SEAT CUSHION-POWER</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>운전석</t>
-        </is>
-      </c>
+          <t>MESH UP/DOWN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1114,24 +1094,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>885IA1</t>
+          <t>8821B2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOLD'G </t>
+          <t>MESH UP/DOWN &amp; SLIDING</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SEAT BACK FOLDING</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>조수석</t>
-        </is>
-      </c>
+          <t>HEAD REST - UP/DOWN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1141,22 +1117,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8854A1 </t>
+          <t xml:space="preserve">8823A1 </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>H_UP/DN</t>
+          <t>SLID'G</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Headrest</t>
+          <t>CUSH MECH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1168,22 +1144,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8854A5</t>
+          <t xml:space="preserve">8823B2 </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>H_SLID'G</t>
+          <t>TOWEL BAR TYPE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Headrest</t>
+          <t>CUSH MECH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1171,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8857A2</t>
+          <t xml:space="preserve">8824A2 </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>H_ADJ</t>
+          <t>D_RECL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1210,7 +1186,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1222,22 +1198,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8862A2</t>
+          <t>8825A2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">PWR </t>
+          <t>H_ADJ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1249,22 +1225,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8859A1</t>
+          <t xml:space="preserve">8827A1 </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODS    </t>
+          <t xml:space="preserve">PWR </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Weight Sensor</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1276,22 +1252,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>885DA1</t>
+          <t xml:space="preserve">8827A3 </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SLID'G</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CUSH MECH</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1303,22 +1279,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>885EA2</t>
+          <t>8828A2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>D_RECL</t>
+          <t>L/SUPT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DOUBLE RECLING</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1330,24 +1306,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>885NA1</t>
+          <t>8828A5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENT </t>
+          <t>L/SUPT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AIR VENTILATION SEAT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>조수석</t>
-        </is>
-      </c>
+          <t>2CELL 4WAY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1357,22 +1329,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>885PA1</t>
+          <t xml:space="preserve">8828A6 </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TABLE  </t>
+          <t>2WAY L/SUPT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FOLD UP TRAY</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1384,22 +1356,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>885JA1</t>
+          <t xml:space="preserve">8836A1 </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>W/IN</t>
+          <t>B/POCKET</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WALK IN S/W</t>
+          <t>SEAT BACK POCKET</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1411,24 +1383,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8889A1 </t>
+          <t>8836A2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SBR</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SEAT BELT REMINDER</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>조수석</t>
-        </is>
-      </c>
+          <t>B/BOARD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1438,18 +1402,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>886BA1</t>
+          <t>8836A3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B/POCKET</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>B/PNL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>W/POCKET</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1461,22 +1429,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>886BA3</t>
+          <t>8838B3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B/PNL</t>
+          <t>HTR(2STEP)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>W/POCKET</t>
+          <t>HTR(HIGH/LOW)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1488,22 +1456,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8873B4</t>
+          <t>8838B4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HTR</t>
+          <t>HTR(3STEP)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3-STEPS (BUTTON)</t>
+          <t>3-STEPS(BUTTON)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>조수석</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1515,22 +1483,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8881B1</t>
+          <t>8839A1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S/BELT</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ELR(DRIVER'S SIDE)</t>
-        </is>
-      </c>
+          <t>EASY ACCESS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>안전부품</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1506,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>888AA2</t>
+          <t>8841A1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P_TENSNR</t>
+          <t>VENT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ELECTRICAL TYPE</t>
+          <t>AIR VENTILATION SEAT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>안전부품</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1569,18 +1533,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>888DA1</t>
+          <t>8845A1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SBR</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t xml:space="preserve">TABLE  </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FOLD UP TRAY</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>안전부품</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1592,22 +1560,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5693A1 </t>
+          <t>8847A2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">THORAX </t>
+          <t>P_EXT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SIDE AIR BAG</t>
+          <t>EXTENDABLE SEAT CUSHION-POWER</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>안전부품</t>
+          <t>운전석</t>
         </is>
       </c>
     </row>
@@ -1619,179 +1587,211 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5693A3</t>
+          <t xml:space="preserve">8854A1 </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T &amp; P</t>
+          <t>H_UP/DN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SIDE AIR BAG</t>
+          <t>Headrest</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>안전부품</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2열</t>
+          <t>1열</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8912C1</t>
+          <t>8854A5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6:4 SPLIT</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>H_SLID'G</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Headrest</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>조수석</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2열</t>
+          <t>1열</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8912H9</t>
+          <t>8857A2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3:3:3 SEAT</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>H_ADJ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MNL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>조수석</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2열</t>
+          <t>1열</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8912D2</t>
+          <t>8859A1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C/BENCH</t>
+          <t xml:space="preserve">ODS    </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>쿠션벤치</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>Weight Sensor</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>조수석</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2열</t>
+          <t>1열</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>891MA1</t>
+          <t>8862A2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>H_FOLD'G</t>
+          <t xml:space="preserve">PWR </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>폴딩 헤드레스트</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>조수석</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2열</t>
+          <t>1열</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>892QA1</t>
+          <t>8873B4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>W/IN</t>
+          <t>HTR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>WALK IN</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>3-STEPS (BUTTON)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>조수석</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2열</t>
+          <t>1열</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>892WB3</t>
+          <t>8881B1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WMR</t>
+          <t>S/BELT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>WARMER</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>ELR(DRIVER'S SIDE)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>안전부품</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2열</t>
+          <t>1열</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8982A1</t>
+          <t xml:space="preserve">8889A1 </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C/BELT(2P)</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CTR벨트 2점식</t>
+          <t>SEAT BELT REMINDER</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>안전부품</t>
+          <t>조수석</t>
         </is>
       </c>
     </row>
@@ -1803,160 +1803,220 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8982A4</t>
+          <t>891MA1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C/BELT(3P)</t>
+          <t>H_FOLD'G</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CTR벨트 3점식</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>안전부품</t>
-        </is>
-      </c>
+          <t>폴딩 헤드레스트</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3열</t>
+          <t>2열</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>893PA1</t>
+          <t>892QA1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>H_FOLD'G</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>W/IN</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>WALK IN</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>2열</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9911A6</t>
+          <t>892WB3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ME SPEC</t>
+          <t>WMR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>일반/중동 스펙</t>
+          <t>WARMER</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2열</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8836A2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>8912C1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>6:4 SPLIT</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2열</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>961SA3</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>8912D2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C/BENCH</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1PORT(2EA)</t>
+          <t>쿠션벤치</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2열</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>882ZA1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>RELAXION SEAT - PREMIUM RELAXION SEAT</t>
-        </is>
-      </c>
+          <t>8912H9</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3:3:3 SEAT</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2열</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8828A5</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>8982A1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C/BELT(2P)</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2CELL 4WAY</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>CTR벨트 2점식</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>안전부품</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2열</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8821B2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>8982A4</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>C/BELT(3P)</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HEAD REST - UP/DOWN</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>CTR벨트 3점식</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>안전부품</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3열</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8821B1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>893PA1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>H_FOLD'G</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5699A1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>9911A6</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ME SPEC</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CENTER SIDE AIR BAG</t>
+          <t>일반/중동 스펙</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1968,7 +2028,11 @@
           <t>0093E6</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GT LINE</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
     </row>
@@ -1979,7 +2043,11 @@
           <t>0093F2</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>X LINE</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
     </row>
@@ -1990,7 +2058,11 @@
           <t>0094A1</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TYPE 1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
     </row>

--- a/EBOM/bom_web/data/pel_code_master.xlsx
+++ b/EBOM/bom_web/data/pel_code_master.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +429,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>사양</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1311,7 +1323,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>L/SUPT</t>
+          <t>L/SUPT(2CELL)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1319,7 +1331,11 @@
           <t>2CELL 4WAY</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>운전석</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1329,17 +1345,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8828A6 </t>
+          <t>8828A6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2WAY L/SUPT</t>
+          <t>L/SUPT(4CELL)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>4CELL 4WAY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
